--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BAUBLOCK GYMNÁSTICA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BAUBLOCK GYMNÁSTICA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>97.7308</v>
+        <v>87.76559999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>77.5107</v>
+        <v>69.34690000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>20.2201</v>
+        <v>18.4191</v>
       </c>
       <c r="G2" t="n">
-        <v>23.9338</v>
+        <v>70.55419999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>42.6136</v>
+        <v>46.2786</v>
       </c>
       <c r="I2" t="n">
-        <v>-18.6799</v>
+        <v>24.2758</v>
       </c>
       <c r="J2" t="n">
-        <v>51.2041</v>
+        <v>97.8302</v>
       </c>
       <c r="K2" t="n">
-        <v>53.7689</v>
+        <v>56.0121</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.5648</v>
+        <v>41.818</v>
       </c>
       <c r="M2" t="n">
-        <v>-27.2703</v>
+        <v>-27.276</v>
       </c>
       <c r="N2" t="n">
-        <v>-11.1554</v>
+        <v>-9.733499999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-16.1151</v>
+        <v>-17.5422</v>
       </c>
       <c r="P2" t="n">
-        <v>5.7439</v>
+        <v>0.9263999999999994</v>
       </c>
       <c r="Q2" t="n">
-        <v>-43.3568</v>
+        <v>-56.1419</v>
       </c>
       <c r="R2" t="n">
-        <v>49.1012</v>
+        <v>57.0686</v>
       </c>
       <c r="S2" t="n">
-        <v>54.835</v>
+        <v>9.121499999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>38.5131</v>
+        <v>2.8138</v>
       </c>
       <c r="U2" t="n">
-        <v>16.3217</v>
+        <v>6.3077</v>
       </c>
       <c r="V2" t="n">
-        <v>13.2183</v>
+        <v>7.1637</v>
       </c>
       <c r="W2" t="n">
-        <v>31.151</v>
+        <v>24.8452</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.9325</v>
+        <v>-17.6816</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>89.4174</v>
+        <v>75.85939999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>65.28579999999999</v>
+        <v>54.0931</v>
       </c>
       <c r="F3" t="n">
-        <v>24.1316</v>
+        <v>21.7667</v>
       </c>
       <c r="G3" t="n">
         <v>36.551</v>
@@ -688,13 +688,13 @@
         <v>44.46879999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>27.7209</v>
+        <v>14.1627</v>
       </c>
       <c r="T3" t="n">
-        <v>17.0608</v>
+        <v>5.8677</v>
       </c>
       <c r="U3" t="n">
-        <v>10.6601</v>
+        <v>8.2951</v>
       </c>
       <c r="V3" t="n">
         <v>26.9983</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>73.929</v>
+        <v>66.7379</v>
       </c>
       <c r="E4" t="n">
-        <v>61.573</v>
+        <v>53.4774</v>
       </c>
       <c r="F4" t="n">
-        <v>12.3562</v>
+        <v>13.2606</v>
       </c>
       <c r="G4" t="n">
-        <v>70.55419999999999</v>
+        <v>23.9338</v>
       </c>
       <c r="H4" t="n">
-        <v>46.2786</v>
+        <v>42.6136</v>
       </c>
       <c r="I4" t="n">
-        <v>24.2758</v>
+        <v>-18.6799</v>
       </c>
       <c r="J4" t="n">
-        <v>97.8302</v>
+        <v>51.2041</v>
       </c>
       <c r="K4" t="n">
-        <v>56.0121</v>
+        <v>53.7689</v>
       </c>
       <c r="L4" t="n">
-        <v>41.818</v>
+        <v>-2.5648</v>
       </c>
       <c r="M4" t="n">
-        <v>-27.276</v>
+        <v>-27.2703</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.733499999999999</v>
+        <v>-11.1554</v>
       </c>
       <c r="O4" t="n">
-        <v>-17.5422</v>
+        <v>-16.1151</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9263999999999994</v>
+        <v>5.7439</v>
       </c>
       <c r="Q4" t="n">
-        <v>-56.1419</v>
+        <v>-43.3568</v>
       </c>
       <c r="R4" t="n">
-        <v>57.0686</v>
+        <v>49.1012</v>
       </c>
       <c r="S4" t="n">
-        <v>-4.715100000000001</v>
+        <v>23.8419</v>
       </c>
       <c r="T4" t="n">
-        <v>-4.9599</v>
+        <v>14.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2448000000000003</v>
+        <v>9.3619</v>
       </c>
       <c r="V4" t="n">
-        <v>7.1637</v>
+        <v>13.2183</v>
       </c>
       <c r="W4" t="n">
-        <v>24.8452</v>
+        <v>31.151</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.6816</v>
+        <v>-17.9325</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>31.0178</v>
+        <v>36.8774</v>
       </c>
       <c r="E5" t="n">
-        <v>37.9344</v>
+        <v>40.996</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.916699999999999</v>
+        <v>-4.1185</v>
       </c>
       <c r="G5" t="n">
         <v>60.8582</v>
@@ -844,13 +844,13 @@
         <v>50.7689</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7356</v>
+        <v>8.5952</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1071</v>
+        <v>4.1688</v>
       </c>
       <c r="U5" t="n">
-        <v>1.628699999999999</v>
+        <v>4.4267</v>
       </c>
       <c r="V5" t="n">
         <v>5.9634</v>
@@ -955,13 +955,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>10.1076</v>
+        <v>8.594200000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>8.7271</v>
+        <v>6.4544</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3808</v>
+        <v>2.1397</v>
       </c>
       <c r="G7" t="n">
         <v>0.9735999999999998</v>
@@ -1000,13 +1000,13 @@
         <v>18.5284</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9156</v>
+        <v>2.4017</v>
       </c>
       <c r="T7" t="n">
-        <v>4.7779</v>
+        <v>2.5053</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8621000000000001</v>
+        <v>-0.1033999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6373</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CALLE GÓMEZ</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>4.7207</v>
+        <v>6.644200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7207</v>
+        <v>0.4242999999999997</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>6.2195</v>
       </c>
       <c r="G8" t="n">
-        <v>4.7207</v>
+        <v>-2.5621</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6103</v>
+        <v>12.2062</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1105</v>
+        <v>-14.7681</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7207</v>
+        <v>26.6099</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6103</v>
+        <v>24.3102</v>
       </c>
       <c r="L8" t="n">
-        <v>3.1105</v>
+        <v>2.2996</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-29.1718</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-12.104</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-17.0677</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>12.7844</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-36.1308</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>48.9159</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-1.0668</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.207</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-4.7189</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>11.0126</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-15.7316</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. CHAGOYEN SALGUERO</t>
+          <t>A. CALLE GÓMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>3.708499999999999</v>
+        <v>4.7207</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8441</v>
+        <v>4.7207</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1356999999999999</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.93</v>
+        <v>4.7207</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7145</v>
+        <v>1.6103</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.6448</v>
+        <v>3.1105</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1674</v>
+        <v>4.7207</v>
       </c>
       <c r="K9" t="n">
-        <v>5.508900000000001</v>
+        <v>1.6103</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.3413</v>
+        <v>3.1105</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.0975</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.7941</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3034</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.335199999999999</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8528</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5.188</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0445</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6416999999999999</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4028</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2588</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CARBU RODRIGUEZ</t>
+          <t>R. VARELA SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>3.140999999999998</v>
+        <v>4.1874</v>
       </c>
       <c r="E10" t="n">
-        <v>5.817500000000001</v>
+        <v>2.8226</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6769</v>
+        <v>1.364900000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4895000000000004</v>
+        <v>15.6749</v>
       </c>
       <c r="H10" t="n">
-        <v>2.33</v>
+        <v>20.3366</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8193</v>
+        <v>-4.6618</v>
       </c>
       <c r="J10" t="n">
-        <v>7.444700000000001</v>
+        <v>30.574</v>
       </c>
       <c r="K10" t="n">
-        <v>5.1733</v>
+        <v>25.3556</v>
       </c>
       <c r="L10" t="n">
-        <v>2.2714</v>
+        <v>5.2185</v>
       </c>
       <c r="M10" t="n">
-        <v>-7.9341</v>
+        <v>-14.8991</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.8435</v>
+        <v>-5.0191</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.090800000000001</v>
+        <v>-9.8802</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1501</v>
+        <v>4.8173</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.7819</v>
+        <v>-30.2016</v>
       </c>
       <c r="R10" t="n">
-        <v>10.9321</v>
+        <v>35.0192</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9408</v>
+        <v>-0.1929999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>4.8971</v>
+        <v>-0.3807</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9563000000000001</v>
+        <v>0.1872</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.4604</v>
+        <v>-16.1115</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2578</v>
+        <v>2.8311</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.7182</v>
+        <v>-18.9426</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>U. CHAGOYEN SALGUERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>2.416700000000001</v>
+        <v>3.9768</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9441</v>
+        <v>3.605</v>
       </c>
       <c r="F11" t="n">
-        <v>6.361000000000001</v>
+        <v>0.3718999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.748699999999999</v>
+        <v>-1.93</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1485</v>
+        <v>2.7145</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.8973</v>
+        <v>-4.6448</v>
       </c>
       <c r="J11" t="n">
-        <v>4.862399999999999</v>
+        <v>3.1674</v>
       </c>
       <c r="K11" t="n">
-        <v>7.8677</v>
+        <v>5.508900000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.0054</v>
+        <v>-2.3413</v>
       </c>
       <c r="M11" t="n">
-        <v>-10.6113</v>
+        <v>-5.0975</v>
       </c>
       <c r="N11" t="n">
-        <v>-6.7195</v>
+        <v>-2.7941</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.8919</v>
+        <v>-2.3034</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4821</v>
+        <v>3.335199999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-19.8257</v>
+        <v>-1.8528</v>
       </c>
       <c r="R11" t="n">
-        <v>21.3082</v>
+        <v>5.188</v>
       </c>
       <c r="S11" t="n">
-        <v>8.254900000000001</v>
+        <v>1.3128</v>
       </c>
       <c r="T11" t="n">
-        <v>5.0404</v>
+        <v>0.4027</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2147</v>
+        <v>0.9102</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5718</v>
+        <v>1.2588</v>
       </c>
       <c r="W11" t="n">
-        <v>5.9788</v>
+        <v>1.8877</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.5505</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GALLARDO</t>
+          <t>A. CALLE GOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04220000000000002</v>
+        <v>2.637</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8540000000000001</v>
+        <v>-1.2662</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8117</v>
+        <v>3.9034</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3253000000000001</v>
+        <v>0.6950000000000005</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0394</v>
+        <v>-0.1077</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7139999999999997</v>
+        <v>0.8027</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5257000000000001</v>
+        <v>3.3671</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2629</v>
+        <v>0.1155</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7371000000000001</v>
+        <v>3.2516</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2004</v>
+        <v>-2.672</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2235</v>
+        <v>-0.2232999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.02300000000000002</v>
+        <v>-2.4491</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5558999999999999</v>
+        <v>4.446899999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-5.3732</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5558999999999999</v>
+        <v>9.8202</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2728</v>
+        <v>0.6416000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3282</v>
+        <v>0.7400000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0554</v>
+        <v>-0.09839999999999993</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-3.1466</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-3.1466</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CALLE GOMEZ</t>
+          <t>J. CARBU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2142</v>
+        <v>2.1431</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.726</v>
+        <v>3.8273</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5116</v>
+        <v>-1.684399999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6950000000000005</v>
+        <v>-0.4895000000000004</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1077</v>
+        <v>2.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8027</v>
+        <v>-2.8193</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3671</v>
+        <v>7.444700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1155</v>
+        <v>5.1733</v>
       </c>
       <c r="L13" t="n">
-        <v>3.2516</v>
+        <v>2.2714</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.672</v>
+        <v>-7.9341</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2232999999999999</v>
+        <v>-2.8435</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.4491</v>
+        <v>-5.090800000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>4.446899999999999</v>
+        <v>3.1501</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.3732</v>
+        <v>-7.7819</v>
       </c>
       <c r="R13" t="n">
-        <v>9.8202</v>
+        <v>10.9321</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.2095</v>
+        <v>2.9428</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7197</v>
+        <v>2.907</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4898</v>
+        <v>0.03610000000000005</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.1466</v>
+        <v>-3.4604</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2578</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.1466</v>
+        <v>-4.7182</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.218900000000002</v>
+        <v>1.1852</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.654</v>
+        <v>-5.2377</v>
       </c>
       <c r="F14" t="n">
-        <v>15.4352</v>
+        <v>6.4229</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.2974</v>
+        <v>-5.748699999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>2.430899999999999</v>
+        <v>1.1485</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.7282</v>
+        <v>-6.8973</v>
       </c>
       <c r="J14" t="n">
-        <v>3.964500000000001</v>
+        <v>4.862399999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>8.0678</v>
+        <v>7.8677</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.103300000000001</v>
+        <v>-3.0054</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.2618</v>
+        <v>-10.6113</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.6371</v>
+        <v>-6.7195</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.6252</v>
+        <v>-3.8919</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4824</v>
+        <v>1.4821</v>
       </c>
       <c r="Q14" t="n">
-        <v>-35.9457</v>
+        <v>-19.8257</v>
       </c>
       <c r="R14" t="n">
-        <v>37.428</v>
+        <v>21.3082</v>
       </c>
       <c r="S14" t="n">
-        <v>5.2898</v>
+        <v>7.0235</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6839000000000001</v>
+        <v>3.7473</v>
       </c>
       <c r="U14" t="n">
-        <v>5.9731</v>
+        <v>3.2765</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6932000000000003</v>
+        <v>-1.5718</v>
       </c>
       <c r="W14" t="n">
-        <v>11.0108</v>
+        <v>5.9788</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.7042</v>
+        <v>-7.5505</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. VARELA SANCHEZ</t>
+          <t>D. RODRIGUEZ GALLARDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.596599999999999</v>
+        <v>0.5032000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.8976</v>
+        <v>-0.5055000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.699000000000001</v>
+        <v>1.0087</v>
       </c>
       <c r="G15" t="n">
-        <v>15.6749</v>
+        <v>-0.3253000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>20.3366</v>
+        <v>-1.0394</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.6618</v>
+        <v>0.7139999999999997</v>
       </c>
       <c r="J15" t="n">
-        <v>30.574</v>
+        <v>-0.5257000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>25.3556</v>
+        <v>-1.2629</v>
       </c>
       <c r="L15" t="n">
-        <v>5.2185</v>
+        <v>0.7371000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-14.8991</v>
+        <v>0.2004</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.0191</v>
+        <v>0.2235</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.8802</v>
+        <v>-0.02300000000000002</v>
       </c>
       <c r="P15" t="n">
-        <v>4.8173</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-30.2016</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>35.0192</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-13.9769</v>
+        <v>0.2726</v>
       </c>
       <c r="T15" t="n">
-        <v>-11.1007</v>
+        <v>0.0202</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.8761</v>
+        <v>0.2525</v>
       </c>
       <c r="V15" t="n">
-        <v>-16.1115</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8311</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-18.9426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.3954</v>
+        <v>-2.3794</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.0268</v>
+        <v>-17.7338</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6315</v>
+        <v>15.3545</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.5621</v>
+        <v>-12.2974</v>
       </c>
       <c r="H16" t="n">
-        <v>12.2062</v>
+        <v>2.430899999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-14.7681</v>
+        <v>-14.7282</v>
       </c>
       <c r="J16" t="n">
-        <v>26.6099</v>
+        <v>3.964500000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>24.3102</v>
+        <v>8.0678</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2996</v>
+        <v>-4.103300000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-29.1718</v>
+        <v>-16.2618</v>
       </c>
       <c r="N16" t="n">
-        <v>-12.104</v>
+        <v>-5.6371</v>
       </c>
       <c r="O16" t="n">
-        <v>-17.0677</v>
+        <v>-10.6252</v>
       </c>
       <c r="P16" t="n">
-        <v>12.7844</v>
+        <v>1.4824</v>
       </c>
       <c r="Q16" t="n">
-        <v>-36.1308</v>
+        <v>-35.9457</v>
       </c>
       <c r="R16" t="n">
-        <v>48.9159</v>
+        <v>37.428</v>
       </c>
       <c r="S16" t="n">
-        <v>-15.899</v>
+        <v>9.129199999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-13.5181</v>
+        <v>3.2365</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.3811</v>
+        <v>5.8929</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.7189</v>
+        <v>-0.6932000000000003</v>
       </c>
       <c r="W16" t="n">
-        <v>11.0126</v>
+        <v>11.0108</v>
       </c>
       <c r="X16" t="n">
-        <v>-15.7316</v>
+        <v>-11.7042</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-33.7732</v>
+        <v>-25.3212</v>
       </c>
       <c r="E17" t="n">
-        <v>-19.7211</v>
+        <v>-13.9634</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.0521</v>
+        <v>-11.358</v>
       </c>
       <c r="G17" t="n">
         <v>-2.5669</v>
@@ -1780,13 +1780,13 @@
         <v>23.1609</v>
       </c>
       <c r="S17" t="n">
-        <v>-8.413399999999999</v>
+        <v>0.03840000000000002</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.6185</v>
+        <v>1.1394</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.7948</v>
+        <v>-1.1006</v>
       </c>
       <c r="V17" t="n">
         <v>-16.6783</v>
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>278.9629</v>
+        <v>298.1454</v>
       </c>
       <c r="E18" t="n">
-        <v>219.6036</v>
+        <v>225.075</v>
       </c>
       <c r="F18" t="n">
-        <v>59.35929999999999</v>
+        <v>73.071</v>
       </c>
       <c r="G18" t="n">
         <v>212.0554</v>
@@ -1831,10 +1831,10 @@
         <v>-48.908</v>
       </c>
       <c r="J18" t="n">
-        <v>433.4748999999999</v>
+        <v>433.4749</v>
       </c>
       <c r="K18" t="n">
-        <v>348.8708999999999</v>
+        <v>348.8709</v>
       </c>
       <c r="L18" t="n">
         <v>84.60329999999999</v>
@@ -1843,7 +1843,7 @@
         <v>-221.4189</v>
       </c>
       <c r="N18" t="n">
-        <v>-87.9088</v>
+        <v>-87.90879999999999</v>
       </c>
       <c r="O18" t="n">
         <v>-133.5117</v>
@@ -1858,16 +1858,16 @@
         <v>412.2642999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>61.2504</v>
+        <v>80.43090000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>35.10910000000001</v>
+        <v>40.5812</v>
       </c>
       <c r="U18" t="n">
-        <v>26.1411</v>
+        <v>39.8514</v>
       </c>
       <c r="V18" t="n">
-        <v>6.584500000000006</v>
+        <v>6.584500000000002</v>
       </c>
       <c r="W18" t="n">
         <v>164.2105</v>
